--- a/Lab_4/data/partB/param_optimization_process/v200_k40_s150_results.xlsx
+++ b/Lab_4/data/partB/param_optimization_process/v200_k40_s150_results.xlsx
@@ -518,49 +518,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
         <v>2</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
+        <v>11</v>
+      </c>
+      <c r="G2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" t="n">
+        <v>39</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2" t="n">
         <v>2</v>
       </c>
-      <c r="F2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G2" t="n">
-        <v>7</v>
-      </c>
-      <c r="H2" t="n">
-        <v>7</v>
-      </c>
-      <c r="I2" t="n">
-        <v>31</v>
-      </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>8</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
         <v>1</v>
       </c>
-      <c r="K2" t="n">
-        <v>6</v>
-      </c>
-      <c r="L2" t="n">
-        <v>2</v>
-      </c>
-      <c r="M2" t="n">
-        <v>6</v>
-      </c>
-      <c r="N2" t="n">
-        <v>7</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -570,13 +570,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
         <v>6</v>
@@ -585,34 +585,34 @@
         <v>1</v>
       </c>
       <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>1</v>
       </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
       <c r="J3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -646,13 +646,13 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -677,46 +677,46 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F5" t="n">
+        <v>12</v>
+      </c>
+      <c r="G5" t="n">
         <v>6</v>
       </c>
-      <c r="G5" t="n">
-        <v>9</v>
-      </c>
       <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" t="n">
         <v>0</v>
       </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>5</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>9</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
+        <v>2</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" t="n">
         <v>4</v>
-      </c>
-      <c r="O5" t="n">
-        <v>2</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
         <v>2</v>
@@ -735,19 +735,19 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G6" t="n">
         <v>12</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -756,16 +756,16 @@
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
         <v>4</v>
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -787,22 +787,22 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="G7" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>2</v>
@@ -811,16 +811,16 @@
         <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -842,16 +842,16 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
+        <v>6</v>
+      </c>
+      <c r="G8" t="n">
         <v>8</v>
       </c>
-      <c r="G8" t="n">
-        <v>13</v>
-      </c>
       <c r="H8" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -860,19 +860,19 @@
         <v>12</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -882,46 +882,46 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G9" t="n">
         <v>4</v>
       </c>
       <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>58</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>5</v>
-      </c>
-      <c r="I9" t="n">
-        <v>49</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>12</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N9" t="n">
+        <v>3</v>
+      </c>
+      <c r="O9" t="n">
         <v>2</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1</v>
       </c>
       <c r="P9" t="n">
         <v>1</v>
@@ -937,13 +937,13 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -955,25 +955,25 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -986,7 +986,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -995,40 +995,40 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G11" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H11" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I11" t="n">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1038,19 +1038,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D12" t="n">
         <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1059,25 +1059,25 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O12" t="n">
         <v>1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>4</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -1090,43 +1090,43 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="N13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O13" t="n">
         <v>4</v>
@@ -1142,49 +1142,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="G14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M14" t="n">
+        <v>7</v>
+      </c>
+      <c r="N14" t="n">
+        <v>39</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
         <v>8</v>
-      </c>
-      <c r="N14" t="n">
-        <v>42</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1</v>
-      </c>
-      <c r="P14" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -1215,7 +1215,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1224,16 +1224,16 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="P15" t="n">
         <v>1</v>
@@ -1246,19 +1246,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F16" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G16" t="n">
         <v>8</v>
@@ -1267,10 +1267,10 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1279,16 +1279,16 @@
         <v>4</v>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O16" t="n">
         <v>2</v>
       </c>
       <c r="P16" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1692,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2899,7 +2899,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -3035,7 +3035,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3273,7 +3273,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3494,7 +3494,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -3732,7 +3732,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -3834,7 +3834,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -3868,7 +3868,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4038,7 +4038,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -4072,7 +4072,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4089,7 +4089,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -4191,7 +4191,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4225,7 +4225,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -4752,7 +4752,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5925,7 +5925,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5959,7 +5959,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -6231,7 +6231,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -6469,7 +6469,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -6571,7 +6571,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -6605,7 +6605,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6639,7 +6639,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -6656,7 +6656,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6792,7 +6792,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6843,7 +6843,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6911,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -6928,7 +6928,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -7013,7 +7013,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7030,7 +7030,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7081,7 +7081,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -7183,7 +7183,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7302,7 +7302,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7370,7 +7370,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7404,7 +7404,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -7540,7 +7540,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7625,7 +7625,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7642,7 +7642,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7693,7 +7693,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7727,7 +7727,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7812,7 +7812,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -7829,7 +7829,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -7880,7 +7880,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7914,7 +7914,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7948,7 +7948,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -7965,7 +7965,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -8050,7 +8050,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -8118,7 +8118,7 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -8203,7 +8203,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -8288,7 +8288,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -8339,7 +8339,7 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -8407,7 +8407,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8424,7 +8424,7 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8475,7 +8475,7 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8509,7 +8509,7 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -8611,7 +8611,7 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -8679,7 +8679,7 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8713,7 +8713,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -8730,7 +8730,7 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8747,7 +8747,7 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8781,7 +8781,7 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8832,7 +8832,7 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8883,7 +8883,7 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9002,7 +9002,7 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -9138,7 +9138,7 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9257,7 +9257,7 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9291,7 +9291,7 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9342,7 +9342,7 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9376,7 +9376,7 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9495,7 +9495,7 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -9546,7 +9546,7 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9733,7 +9733,7 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9801,7 +9801,7 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9835,7 +9835,7 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10005,7 +10005,7 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10175,7 +10175,7 @@
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10345,7 +10345,7 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -10413,7 +10413,7 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -10532,7 +10532,7 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -10617,7 +10617,7 @@
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10634,7 +10634,7 @@
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -10685,7 +10685,7 @@
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10719,7 +10719,7 @@
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10770,7 +10770,7 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10923,7 +10923,7 @@
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11042,7 +11042,7 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11212,7 +11212,7 @@
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11314,7 +11314,7 @@
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11348,7 +11348,7 @@
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -11399,7 +11399,7 @@
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -11416,7 +11416,7 @@
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11433,7 +11433,7 @@
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11467,7 +11467,7 @@
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11501,7 +11501,7 @@
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11518,7 +11518,7 @@
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11535,7 +11535,7 @@
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11671,7 +11671,7 @@
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11688,7 +11688,7 @@
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -11722,7 +11722,7 @@
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -11739,7 +11739,7 @@
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11824,7 +11824,7 @@
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -11841,7 +11841,7 @@
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -11892,7 +11892,7 @@
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -11994,7 +11994,7 @@
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12045,7 +12045,7 @@
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12096,7 +12096,7 @@
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12181,7 +12181,7 @@
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12215,7 +12215,7 @@
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12283,7 +12283,7 @@
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -12300,7 +12300,7 @@
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12334,7 +12334,7 @@
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12368,7 +12368,7 @@
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12436,7 +12436,7 @@
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12470,7 +12470,7 @@
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12521,7 +12521,7 @@
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12555,7 +12555,7 @@
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12623,7 +12623,7 @@
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12640,7 +12640,7 @@
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12725,7 +12725,7 @@
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12776,7 +12776,7 @@
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -12861,7 +12861,7 @@
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -12878,7 +12878,7 @@
       </c>
       <c r="C681" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12895,7 +12895,7 @@
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -12912,7 +12912,7 @@
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12929,7 +12929,7 @@
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12963,7 +12963,7 @@
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -12980,7 +12980,7 @@
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12997,7 +12997,7 @@
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13082,7 +13082,7 @@
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13133,7 +13133,7 @@
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13184,7 +13184,7 @@
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13201,7 +13201,7 @@
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13252,7 +13252,7 @@
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13269,7 +13269,7 @@
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -13320,7 +13320,7 @@
       </c>
       <c r="C707" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13337,7 +13337,7 @@
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13422,7 +13422,7 @@
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -13456,7 +13456,7 @@
       </c>
       <c r="C715" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13490,7 +13490,7 @@
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13507,7 +13507,7 @@
       </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -13541,7 +13541,7 @@
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13575,7 +13575,7 @@
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13626,7 +13626,7 @@
       </c>
       <c r="C725" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13677,7 +13677,7 @@
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -13779,7 +13779,7 @@
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13813,7 +13813,7 @@
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13830,7 +13830,7 @@
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13847,7 +13847,7 @@
       </c>
       <c r="C738" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="C743" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -14000,7 +14000,7 @@
       </c>
       <c r="C747" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="C749" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14051,7 +14051,7 @@
       </c>
       <c r="C750" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14102,7 +14102,7 @@
       </c>
       <c r="C753" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14187,7 +14187,7 @@
       </c>
       <c r="C758" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14221,7 +14221,7 @@
       </c>
       <c r="C760" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14272,7 +14272,7 @@
       </c>
       <c r="C763" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14340,7 +14340,7 @@
       </c>
       <c r="C767" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -14374,7 +14374,7 @@
       </c>
       <c r="C769" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14408,7 +14408,7 @@
       </c>
       <c r="C771" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14442,7 +14442,7 @@
       </c>
       <c r="C773" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -14476,7 +14476,7 @@
       </c>
       <c r="C775" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14510,7 +14510,7 @@
       </c>
       <c r="C777" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -14527,7 +14527,7 @@
       </c>
       <c r="C778" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14544,7 +14544,7 @@
       </c>
       <c r="C779" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -14561,7 +14561,7 @@
       </c>
       <c r="C780" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14578,7 +14578,7 @@
       </c>
       <c r="C781" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14714,7 +14714,7 @@
       </c>
       <c r="C789" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -14765,7 +14765,7 @@
       </c>
       <c r="C792" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14782,7 +14782,7 @@
       </c>
       <c r="C793" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -14799,7 +14799,7 @@
       </c>
       <c r="C794" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14833,7 +14833,7 @@
       </c>
       <c r="C796" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -14867,7 +14867,7 @@
       </c>
       <c r="C798" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14884,7 +14884,7 @@
       </c>
       <c r="C799" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14918,7 +14918,7 @@
       </c>
       <c r="C801" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14969,7 +14969,7 @@
       </c>
       <c r="C804" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15003,7 +15003,7 @@
       </c>
       <c r="C806" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15071,7 +15071,7 @@
       </c>
       <c r="C810" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15105,7 +15105,7 @@
       </c>
       <c r="C812" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15190,7 +15190,7 @@
       </c>
       <c r="C817" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15207,7 +15207,7 @@
       </c>
       <c r="C818" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15224,7 +15224,7 @@
       </c>
       <c r="C819" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15241,7 +15241,7 @@
       </c>
       <c r="C820" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15258,7 +15258,7 @@
       </c>
       <c r="C821" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -15309,7 +15309,7 @@
       </c>
       <c r="C824" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15326,7 +15326,7 @@
       </c>
       <c r="C825" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15394,7 +15394,7 @@
       </c>
       <c r="C829" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15411,7 +15411,7 @@
       </c>
       <c r="C830" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15428,7 +15428,7 @@
       </c>
       <c r="C831" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -15496,7 +15496,7 @@
       </c>
       <c r="C835" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -15513,7 +15513,7 @@
       </c>
       <c r="C836" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15666,7 +15666,7 @@
       </c>
       <c r="C845" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -15734,7 +15734,7 @@
       </c>
       <c r="C849" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15785,7 +15785,7 @@
       </c>
       <c r="C852" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -15802,7 +15802,7 @@
       </c>
       <c r="C853" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15904,7 +15904,7 @@
       </c>
       <c r="C859" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -16023,7 +16023,7 @@
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16074,7 +16074,7 @@
       </c>
       <c r="C869" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16142,7 +16142,7 @@
       </c>
       <c r="C873" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16193,7 +16193,7 @@
       </c>
       <c r="C876" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16261,7 +16261,7 @@
       </c>
       <c r="C880" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -16329,7 +16329,7 @@
       </c>
       <c r="C884" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16363,7 +16363,7 @@
       </c>
       <c r="C886" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16380,7 +16380,7 @@
       </c>
       <c r="C887" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -16431,7 +16431,7 @@
       </c>
       <c r="C890" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16448,7 +16448,7 @@
       </c>
       <c r="C891" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16499,7 +16499,7 @@
       </c>
       <c r="C894" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -16533,7 +16533,7 @@
       </c>
       <c r="C896" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16567,7 +16567,7 @@
       </c>
       <c r="C898" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16635,7 +16635,7 @@
       </c>
       <c r="C902" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -16652,7 +16652,7 @@
       </c>
       <c r="C903" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -16686,7 +16686,7 @@
       </c>
       <c r="C905" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -16737,7 +16737,7 @@
       </c>
       <c r="C908" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -16771,7 +16771,7 @@
       </c>
       <c r="C910" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -16890,7 +16890,7 @@
       </c>
       <c r="C917" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C918" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -16941,7 +16941,7 @@
       </c>
       <c r="C920" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17060,7 +17060,7 @@
       </c>
       <c r="C927" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17094,7 +17094,7 @@
       </c>
       <c r="C929" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17111,7 +17111,7 @@
       </c>
       <c r="C930" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17128,7 +17128,7 @@
       </c>
       <c r="C931" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17145,7 +17145,7 @@
       </c>
       <c r="C932" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -17213,7 +17213,7 @@
       </c>
       <c r="C936" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17247,7 +17247,7 @@
       </c>
       <c r="C938" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -17264,7 +17264,7 @@
       </c>
       <c r="C939" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17298,7 +17298,7 @@
       </c>
       <c r="C941" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -17349,7 +17349,7 @@
       </c>
       <c r="C944" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17366,7 +17366,7 @@
       </c>
       <c r="C945" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17383,7 +17383,7 @@
       </c>
       <c r="C946" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17400,7 +17400,7 @@
       </c>
       <c r="C947" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -17434,7 +17434,7 @@
       </c>
       <c r="C949" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17553,7 +17553,7 @@
       </c>
       <c r="C956" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17587,7 +17587,7 @@
       </c>
       <c r="C958" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="C959" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17638,7 +17638,7 @@
       </c>
       <c r="C961" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17672,7 +17672,7 @@
       </c>
       <c r="C963" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17689,7 +17689,7 @@
       </c>
       <c r="C964" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17757,7 +17757,7 @@
       </c>
       <c r="C968" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17859,7 +17859,7 @@
       </c>
       <c r="C974" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17876,7 +17876,7 @@
       </c>
       <c r="C975" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17927,7 +17927,7 @@
       </c>
       <c r="C978" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17944,7 +17944,7 @@
       </c>
       <c r="C979" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17961,7 +17961,7 @@
       </c>
       <c r="C980" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -17995,7 +17995,7 @@
       </c>
       <c r="C982" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -18029,7 +18029,7 @@
       </c>
       <c r="C984" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -18063,7 +18063,7 @@
       </c>
       <c r="C986" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -18080,7 +18080,7 @@
       </c>
       <c r="C987" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -18199,7 +18199,7 @@
       </c>
       <c r="C994" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -18233,7 +18233,7 @@
       </c>
       <c r="C996" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -18267,7 +18267,7 @@
       </c>
       <c r="C998" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18318,7 +18318,7 @@
       </c>
       <c r="C1001" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18369,7 +18369,7 @@
       </c>
       <c r="C1004" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18386,7 +18386,7 @@
       </c>
       <c r="C1005" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18420,7 +18420,7 @@
       </c>
       <c r="C1007" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18437,7 +18437,7 @@
       </c>
       <c r="C1008" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18454,7 +18454,7 @@
       </c>
       <c r="C1009" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18471,7 +18471,7 @@
       </c>
       <c r="C1010" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18522,7 +18522,7 @@
       </c>
       <c r="C1013" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18539,7 +18539,7 @@
       </c>
       <c r="C1014" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -18607,7 +18607,7 @@
       </c>
       <c r="C1018" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18624,7 +18624,7 @@
       </c>
       <c r="C1019" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18658,7 +18658,7 @@
       </c>
       <c r="C1021" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18692,7 +18692,7 @@
       </c>
       <c r="C1023" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="C1024" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18726,7 +18726,7 @@
       </c>
       <c r="C1025" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18743,7 +18743,7 @@
       </c>
       <c r="C1026" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18760,7 +18760,7 @@
       </c>
       <c r="C1027" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18845,7 +18845,7 @@
       </c>
       <c r="C1032" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18879,7 +18879,7 @@
       </c>
       <c r="C1034" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18896,7 +18896,7 @@
       </c>
       <c r="C1035" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -18930,7 +18930,7 @@
       </c>
       <c r="C1037" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18947,7 +18947,7 @@
       </c>
       <c r="C1038" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19032,7 +19032,7 @@
       </c>
       <c r="C1043" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19066,7 +19066,7 @@
       </c>
       <c r="C1045" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19151,7 +19151,7 @@
       </c>
       <c r="C1050" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -19168,7 +19168,7 @@
       </c>
       <c r="C1051" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19202,7 +19202,7 @@
       </c>
       <c r="C1053" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -19236,7 +19236,7 @@
       </c>
       <c r="C1055" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19253,7 +19253,7 @@
       </c>
       <c r="C1056" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -19270,7 +19270,7 @@
       </c>
       <c r="C1057" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19287,7 +19287,7 @@
       </c>
       <c r="C1058" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19338,7 +19338,7 @@
       </c>
       <c r="C1061" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -19389,7 +19389,7 @@
       </c>
       <c r="C1064" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19406,7 +19406,7 @@
       </c>
       <c r="C1065" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19542,7 +19542,7 @@
       </c>
       <c r="C1073" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -19559,7 +19559,7 @@
       </c>
       <c r="C1074" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="C1076" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -19644,7 +19644,7 @@
       </c>
       <c r="C1079" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19712,7 +19712,7 @@
       </c>
       <c r="C1083" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -19746,7 +19746,7 @@
       </c>
       <c r="C1085" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19763,7 +19763,7 @@
       </c>
       <c r="C1086" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19780,7 +19780,7 @@
       </c>
       <c r="C1087" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19882,7 +19882,7 @@
       </c>
       <c r="C1093" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19899,7 +19899,7 @@
       </c>
       <c r="C1094" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19933,7 +19933,7 @@
       </c>
       <c r="C1096" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19984,7 +19984,7 @@
       </c>
       <c r="C1099" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -20001,7 +20001,7 @@
       </c>
       <c r="C1100" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -20103,7 +20103,7 @@
       </c>
       <c r="C1106" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20137,7 +20137,7 @@
       </c>
       <c r="C1108" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="C1109" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -20205,7 +20205,7 @@
       </c>
       <c r="C1112" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -20239,7 +20239,7 @@
       </c>
       <c r="C1114" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -20443,7 +20443,7 @@
       </c>
       <c r="C1126" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20528,7 +20528,7 @@
       </c>
       <c r="C1131" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20562,7 +20562,7 @@
       </c>
       <c r="C1133" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -20647,7 +20647,7 @@
       </c>
       <c r="C1138" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -20834,7 +20834,7 @@
       </c>
       <c r="C1149" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -20851,7 +20851,7 @@
       </c>
       <c r="C1150" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20885,7 +20885,7 @@
       </c>
       <c r="C1152" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20902,7 +20902,7 @@
       </c>
       <c r="C1153" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -20953,7 +20953,7 @@
       </c>
       <c r="C1156" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -20987,7 +20987,7 @@
       </c>
       <c r="C1158" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -21038,7 +21038,7 @@
       </c>
       <c r="C1161" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21055,7 +21055,7 @@
       </c>
       <c r="C1162" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -21225,7 +21225,7 @@
       </c>
       <c r="C1172" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21293,7 +21293,7 @@
       </c>
       <c r="C1176" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21310,7 +21310,7 @@
       </c>
       <c r="C1177" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -21378,7 +21378,7 @@
       </c>
       <c r="C1181" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21412,7 +21412,7 @@
       </c>
       <c r="C1183" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21582,7 +21582,7 @@
       </c>
       <c r="C1193" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -21650,7 +21650,7 @@
       </c>
       <c r="C1197" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21701,7 +21701,7 @@
       </c>
       <c r="C1200" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21718,7 +21718,7 @@
       </c>
       <c r="C1201" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -21735,7 +21735,7 @@
       </c>
       <c r="C1202" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21786,7 +21786,7 @@
       </c>
       <c r="C1205" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21837,7 +21837,7 @@
       </c>
       <c r="C1208" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -21871,7 +21871,7 @@
       </c>
       <c r="C1210" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21922,7 +21922,7 @@
       </c>
       <c r="C1213" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22007,7 +22007,7 @@
       </c>
       <c r="C1218" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22075,7 +22075,7 @@
       </c>
       <c r="C1222" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22160,7 +22160,7 @@
       </c>
       <c r="C1227" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -22177,7 +22177,7 @@
       </c>
       <c r="C1228" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22194,7 +22194,7 @@
       </c>
       <c r="C1229" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22211,7 +22211,7 @@
       </c>
       <c r="C1230" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22296,7 +22296,7 @@
       </c>
       <c r="C1235" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22415,7 +22415,7 @@
       </c>
       <c r="C1242" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22432,7 +22432,7 @@
       </c>
       <c r="C1243" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22449,7 +22449,7 @@
       </c>
       <c r="C1244" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22568,7 +22568,7 @@
       </c>
       <c r="C1251" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22636,7 +22636,7 @@
       </c>
       <c r="C1255" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22670,7 +22670,7 @@
       </c>
       <c r="C1257" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22721,7 +22721,7 @@
       </c>
       <c r="C1260" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -22823,7 +22823,7 @@
       </c>
       <c r="C1266" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -22840,7 +22840,7 @@
       </c>
       <c r="C1267" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -22891,7 +22891,7 @@
       </c>
       <c r="C1270" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22908,7 +22908,7 @@
       </c>
       <c r="C1271" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -22959,7 +22959,7 @@
       </c>
       <c r="C1274" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22993,7 +22993,7 @@
       </c>
       <c r="C1276" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -23010,7 +23010,7 @@
       </c>
       <c r="C1277" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23044,7 +23044,7 @@
       </c>
       <c r="C1279" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -23061,7 +23061,7 @@
       </c>
       <c r="C1280" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23197,7 +23197,7 @@
       </c>
       <c r="C1288" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -23282,7 +23282,7 @@
       </c>
       <c r="C1293" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -23350,7 +23350,7 @@
       </c>
       <c r="C1297" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -23367,7 +23367,7 @@
       </c>
       <c r="C1298" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -23401,7 +23401,7 @@
       </c>
       <c r="C1300" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -23418,7 +23418,7 @@
       </c>
       <c r="C1301" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23792,7 +23792,7 @@
       </c>
       <c r="C1323" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -23860,7 +23860,7 @@
       </c>
       <c r="C1327" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -23877,7 +23877,7 @@
       </c>
       <c r="C1328" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -23928,7 +23928,7 @@
       </c>
       <c r="C1331" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -23979,7 +23979,7 @@
       </c>
       <c r="C1334" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24047,7 +24047,7 @@
       </c>
       <c r="C1338" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24234,7 +24234,7 @@
       </c>
       <c r="C1349" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -24370,7 +24370,7 @@
       </c>
       <c r="C1357" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -24608,7 +24608,7 @@
       </c>
       <c r="C1371" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -24761,7 +24761,7 @@
       </c>
       <c r="C1380" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24795,7 +24795,7 @@
       </c>
       <c r="C1382" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24812,7 +24812,7 @@
       </c>
       <c r="C1383" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24982,7 +24982,7 @@
       </c>
       <c r="C1393" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -25016,7 +25016,7 @@
       </c>
       <c r="C1395" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25050,7 +25050,7 @@
       </c>
       <c r="C1397" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25067,7 +25067,7 @@
       </c>
       <c r="C1398" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25118,7 +25118,7 @@
       </c>
       <c r="C1401" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25203,7 +25203,7 @@
       </c>
       <c r="C1406" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25220,7 +25220,7 @@
       </c>
       <c r="C1407" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25271,7 +25271,7 @@
       </c>
       <c r="C1410" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25288,7 +25288,7 @@
       </c>
       <c r="C1411" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25373,7 +25373,7 @@
       </c>
       <c r="C1416" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -25492,7 +25492,7 @@
       </c>
       <c r="C1423" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25509,7 +25509,7 @@
       </c>
       <c r="C1424" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25560,7 +25560,7 @@
       </c>
       <c r="C1427" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -25594,7 +25594,7 @@
       </c>
       <c r="C1429" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25628,7 +25628,7 @@
       </c>
       <c r="C1431" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -25645,7 +25645,7 @@
       </c>
       <c r="C1432" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25662,7 +25662,7 @@
       </c>
       <c r="C1433" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -25696,7 +25696,7 @@
       </c>
       <c r="C1435" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25730,7 +25730,7 @@
       </c>
       <c r="C1437" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25798,7 +25798,7 @@
       </c>
       <c r="C1441" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -25985,7 +25985,7 @@
       </c>
       <c r="C1452" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -26087,7 +26087,7 @@
       </c>
       <c r="C1458" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26104,7 +26104,7 @@
       </c>
       <c r="C1459" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26155,7 +26155,7 @@
       </c>
       <c r="C1462" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -26172,7 +26172,7 @@
       </c>
       <c r="C1463" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -26240,7 +26240,7 @@
       </c>
       <c r="C1467" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -26308,7 +26308,7 @@
       </c>
       <c r="C1471" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26325,7 +26325,7 @@
       </c>
       <c r="C1472" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -26393,7 +26393,7 @@
       </c>
       <c r="C1476" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -26410,7 +26410,7 @@
       </c>
       <c r="C1477" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -26427,7 +26427,7 @@
       </c>
       <c r="C1478" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -26478,7 +26478,7 @@
       </c>
       <c r="C1481" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -26529,7 +26529,7 @@
       </c>
       <c r="C1484" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -26580,7 +26580,7 @@
       </c>
       <c r="C1487" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -26597,7 +26597,7 @@
       </c>
       <c r="C1488" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -26614,7 +26614,7 @@
       </c>
       <c r="C1489" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -26682,7 +26682,7 @@
       </c>
       <c r="C1493" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26733,7 +26733,7 @@
       </c>
       <c r="C1496" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26750,7 +26750,7 @@
       </c>
       <c r="C1497" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -26767,7 +26767,7 @@
       </c>
       <c r="C1498" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
